--- a/data/trans_orig/P57B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con bienestar emocional por debajo del percentil 15 (Bericat) en 2023</t>
+          <t>Población con peor bienestar socioemocional (percentil 15) (Bericat) en 2023 (tasa de respuesta: 98,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77152</t>
+          <t>75783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110324</t>
+          <t>110277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106307</t>
+          <t>106241</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134882</t>
+          <t>134696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189629</t>
+          <t>190247</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234206</t>
+          <t>234129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>514459</t>
+          <t>514506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>547631</t>
+          <t>549000</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>522379</t>
+          <t>522565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>550954</t>
+          <t>551020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1047838</t>
+          <t>1047915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1092415</t>
+          <t>1091797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47226</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124003</t>
+          <t>122917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>133102</t>
+          <t>133372</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168762</t>
+          <t>168103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167501</t>
+          <t>157969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>282571</t>
+          <t>283306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1061776</t>
+          <t>1062862</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1138553</t>
+          <t>1138295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>773234</t>
+          <t>773893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>808894</t>
+          <t>808624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1845203</t>
+          <t>1844468</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1960273</t>
+          <t>1969805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53671</t>
+          <t>52925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59298</t>
+          <t>59299</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30056</t>
+          <t>29434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82643</t>
+          <t>83873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62064</t>
+          <t>62835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123497</t>
+          <t>123938</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>637931</t>
+          <t>638677</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662020</t>
+          <t>663913</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>841046</t>
+          <t>839817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>893633</t>
+          <t>894256</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1491794</t>
+          <t>1491353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1553227</t>
+          <t>1552456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>923689</t>
+          <t>923690</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>923689</t>
+          <t>923690</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>923689</t>
+          <t>923690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82155</t>
+          <t>84013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>118175</t>
+          <t>119749</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124451</t>
+          <t>127083</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>180963</t>
+          <t>181355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>229774</t>
+          <t>226789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>291510</t>
+          <t>288200</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>796214</t>
+          <t>794640</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>832234</t>
+          <t>830376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>898396</t>
+          <t>898004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>954908</t>
+          <t>952276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1702238</t>
+          <t>1705548</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1763974</t>
+          <t>1766959</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>254253</t>
+          <t>254826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>365385</t>
+          <t>366914</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>397967</t>
+          <t>397866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>539590</t>
+          <t>534397</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>691136</t>
+          <t>704388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>875819</t>
+          <t>881414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3051168</t>
+          <t>3049639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3162300</t>
+          <t>3161727</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3062715</t>
+          <t>3067908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3204338</t>
+          <t>3204439</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6143039</t>
+          <t>6137444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6327722</t>
+          <t>6314470</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57B_R-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>92287</t>
+          <t>99269</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>75783</t>
+          <t>82974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>110277</t>
+          <t>117258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>119989</t>
+          <t>127298</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106241</t>
+          <t>113184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134696</t>
+          <t>143604</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>212276</t>
+          <t>226568</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>190247</t>
+          <t>205369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234129</t>
+          <t>248877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>532496</t>
+          <t>579962</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>514506</t>
+          <t>561973</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>549000</t>
+          <t>596257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>537272</t>
+          <t>586520</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>522565</t>
+          <t>570214</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>551020</t>
+          <t>600634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1069768</t>
+          <t>1166481</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1047915</t>
+          <t>1144172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1091797</t>
+          <t>1187680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,26%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>624783</t>
+          <t>679231</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>624783</t>
+          <t>679231</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>624783</t>
+          <t>679231</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>657261</t>
+          <t>713818</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>657261</t>
+          <t>713818</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>657261</t>
+          <t>713818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1282044</t>
+          <t>1393049</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1282044</t>
+          <t>1393049</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1282044</t>
+          <t>1393049</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91874</t>
+          <t>102423</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47484</t>
+          <t>85029</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122917</t>
+          <t>122338</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>149533</t>
+          <t>169593</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>133372</t>
+          <t>149731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168103</t>
+          <t>189457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>241407</t>
+          <t>272016</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>157969</t>
+          <t>247437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>283306</t>
+          <t>304108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1093905</t>
+          <t>938646</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1062862</t>
+          <t>918731</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1138295</t>
+          <t>956040</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>792463</t>
+          <t>883769</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>773893</t>
+          <t>863905</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>808624</t>
+          <t>903631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1886367</t>
+          <t>1822415</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1844468</t>
+          <t>1790323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1969805</t>
+          <t>1846994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1185779</t>
+          <t>1041069</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1185779</t>
+          <t>1041069</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1185779</t>
+          <t>1041069</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>941996</t>
+          <t>1053362</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>941996</t>
+          <t>1053362</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>941996</t>
+          <t>1053362</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2127774</t>
+          <t>2094431</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2127774</t>
+          <t>2094431</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2127774</t>
+          <t>2094431</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39198</t>
+          <t>44186</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52925</t>
+          <t>61185</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59299</t>
+          <t>69090</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>55751</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83873</t>
+          <t>86451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>98496</t>
+          <t>113276</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62835</t>
+          <t>94277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123938</t>
+          <t>135261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>652404</t>
+          <t>741121</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>638677</t>
+          <t>724122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663913</t>
+          <t>752811</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>864391</t>
+          <t>732269</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>839817</t>
+          <t>714908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>894256</t>
+          <t>745608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1516795</t>
+          <t>1473390</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1491353</t>
+          <t>1451405</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1552456</t>
+          <t>1492389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>691602</t>
+          <t>785307</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>691602</t>
+          <t>785307</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>691602</t>
+          <t>785307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>923690</t>
+          <t>801359</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>923690</t>
+          <t>801359</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>923690</t>
+          <t>801359</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1615291</t>
+          <t>1586666</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1615291</t>
+          <t>1586666</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1615291</t>
+          <t>1586666</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>100269</t>
+          <t>110033</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84013</t>
+          <t>92611</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119749</t>
+          <t>131123</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>158662</t>
+          <t>175551</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>127083</t>
+          <t>155943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>181355</t>
+          <t>197688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>258931</t>
+          <t>285584</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>226789</t>
+          <t>261168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>288200</t>
+          <t>315018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>814120</t>
+          <t>867860</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>794640</t>
+          <t>846770</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>830376</t>
+          <t>885282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>920697</t>
+          <t>926533</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>898004</t>
+          <t>904396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>952276</t>
+          <t>946141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1734817</t>
+          <t>1794394</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1705548</t>
+          <t>1764960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1766959</t>
+          <t>1818810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>914389</t>
+          <t>977893</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>914389</t>
+          <t>977893</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>914389</t>
+          <t>977893</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1079359</t>
+          <t>1102084</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1079359</t>
+          <t>1102084</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1079359</t>
+          <t>1102084</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1993748</t>
+          <t>2079978</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1993748</t>
+          <t>2079978</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1993748</t>
+          <t>2079978</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>323628</t>
+          <t>355911</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>254826</t>
+          <t>321937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>366914</t>
+          <t>393887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>487482</t>
+          <t>541532</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>397866</t>
+          <t>505520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>534397</t>
+          <t>575781</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>811110</t>
+          <t>897443</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>704388</t>
+          <t>850906</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>881414</t>
+          <t>949298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3092925</t>
+          <t>3127590</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3049639</t>
+          <t>3089614</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3161727</t>
+          <t>3161564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3114823</t>
+          <t>3129091</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3067908</t>
+          <t>3094842</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3204439</t>
+          <t>3165103</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6207748</t>
+          <t>6256681</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6137444</t>
+          <t>6204826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6314470</t>
+          <t>6303218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,11%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3416553</t>
+          <t>3483501</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3416553</t>
+          <t>3483501</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3416553</t>
+          <t>3483501</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3602305</t>
+          <t>3670623</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3602305</t>
+          <t>3670623</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3602305</t>
+          <t>3670623</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7154124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7154124</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7018858</t>
+          <t>7154124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
